--- a/etf_holdings/2026-09-03_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-03_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M437"/>
+  <dimension ref="A1:M327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:00</t>
+          <t>2026-09-03 00:54:13</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17788,7 +17788,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19801,7 +19801,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19984,7 +19984,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20408,6716 +20408,6 @@
         </is>
       </c>
       <c r="M327" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D328" t="n">
-        <v>1</v>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>2330台積電</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>-2.25%2385</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-2.25%</t>
-        </is>
-      </c>
-      <c r="H328" t="n">
-        <v>2385</v>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>8.39%363,000</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>8.39%</t>
-        </is>
-      </c>
-      <c r="K328" t="n">
-        <v>363000</v>
-      </c>
-      <c r="L328" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D329" t="n">
-        <v>1</v>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>6223旺矽</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-2.22%5290</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-2.22%</t>
-        </is>
-      </c>
-      <c r="H329" t="n">
-        <v>5290</v>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>5.92%115,000</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>5.92%</t>
-        </is>
-      </c>
-      <c r="K329" t="n">
-        <v>115000</v>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D330" t="n">
-        <v>1</v>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>2383台光電子</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-3.46%5445</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-3.46%</t>
-        </is>
-      </c>
-      <c r="H330" t="n">
-        <v>5445</v>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>5.68%106,000</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>5.68%</t>
-        </is>
-      </c>
-      <c r="K330" t="n">
-        <v>106000</v>
-      </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>1</v>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>3017奇鋐</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-2.93%3310</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>-2.93%</t>
-        </is>
-      </c>
-      <c r="H331" t="n">
-        <v>3310</v>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>4.34%134,000</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>4.34%</t>
-        </is>
-      </c>
-      <c r="K331" t="n">
-        <v>134000</v>
-      </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D332" t="n">
-        <v>1</v>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>3037欣興</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>+0.21%973</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="H332" t="n">
-        <v>973</v>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>4.19%454,000</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>4.19%</t>
-        </is>
-      </c>
-      <c r="K332" t="n">
-        <v>454000</v>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D333" t="n">
-        <v>1</v>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>2454聯發科</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>-0.93%4275</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="H333" t="n">
-        <v>4275</v>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>4.18%102,000</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>4.18%</t>
-        </is>
-      </c>
-      <c r="K333" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D334" t="n">
-        <v>1</v>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>2059川湖</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>-2.01%13865</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>-2.01%</t>
-        </is>
-      </c>
-      <c r="H334" t="n">
-        <v>13865</v>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>4.04%30,000</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="K334" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D335" t="n">
-        <v>1</v>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>2408南亞科</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>0%518</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H335" t="n">
-        <v>518</v>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>3.76%763,000</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
-      <c r="K335" t="n">
-        <v>763000</v>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D336" t="n">
-        <v>1</v>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>6669緯穎</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>0%2610</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H336" t="n">
-        <v>2610</v>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>3.49%47,000</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="K336" t="n">
-        <v>47000</v>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D337" t="n">
-        <v>1</v>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>6274台燿</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>-2.76%1410</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>-2.76%</t>
-        </is>
-      </c>
-      <c r="H337" t="n">
-        <v>1410</v>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>3.43%249,000</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>3.43%</t>
-        </is>
-      </c>
-      <c r="K337" t="n">
-        <v>249000</v>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D338" t="n">
-        <v>1</v>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>5274信驊科技</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>+3.53%17725</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>+3.53%</t>
-        </is>
-      </c>
-      <c r="H338" t="n">
-        <v>17725</v>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>3.35%20,600</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-      <c r="K338" t="n">
-        <v>20600</v>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D339" t="n">
-        <v>1</v>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>2345智邦</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>-2.95%2140</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
-        </is>
-      </c>
-      <c r="H339" t="n">
-        <v>2140</v>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>2.94%140,000</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="K339" t="n">
-        <v>140000</v>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D340" t="n">
-        <v>1</v>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>3443創意電子</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>-1.67%5895</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>-1.67%</t>
-        </is>
-      </c>
-      <c r="H340" t="n">
-        <v>5895</v>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>2.85%50,000</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>2.85%</t>
-        </is>
-      </c>
-      <c r="K340" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D341" t="n">
-        <v>1</v>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>3189景碩科技</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>-3.09%847</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>-3.09%</t>
-        </is>
-      </c>
-      <c r="H341" t="n">
-        <v>847</v>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>2.53%304,000</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>2.53%</t>
-        </is>
-      </c>
-      <c r="K341" t="n">
-        <v>304000</v>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:42</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D342" t="n">
-        <v>1</v>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>8046南電</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-2.04%1200</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>-2.04%</t>
-        </is>
-      </c>
-      <c r="H342" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>2.52%216,000</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>2.52%</t>
-        </is>
-      </c>
-      <c r="K342" t="n">
-        <v>216000</v>
-      </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D343" t="n">
-        <v>2</v>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>2344華邦電子</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>+1.7%179</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>+1.7%</t>
-        </is>
-      </c>
-      <c r="H343" t="n">
-        <v>179</v>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>2.50%1,496,000</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="K343" t="n">
-        <v>1496000</v>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D344" t="n">
-        <v>2</v>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>6515穎崴</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>+2.03%7050</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>+2.03%</t>
-        </is>
-      </c>
-      <c r="H344" t="n">
-        <v>7050</v>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>2.23%34,000</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="K344" t="n">
-        <v>34000</v>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D345" t="n">
-        <v>2</v>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>3665貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>-6.26%2170</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>-6.26%</t>
-        </is>
-      </c>
-      <c r="H345" t="n">
-        <v>2170</v>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>1.98%90,000</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="K345" t="n">
-        <v>90000</v>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D346" t="n">
-        <v>2</v>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>2308台達電子</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>-7.24%1730</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>-7.24%</t>
-        </is>
-      </c>
-      <c r="H346" t="n">
-        <v>1730</v>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>1.95%110,000</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="K346" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D347" t="n">
-        <v>2</v>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>1303南亞</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>+1.28%237.5</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>+1.28%</t>
-        </is>
-      </c>
-      <c r="H347" t="n">
-        <v>237.5</v>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>1.83%821,000</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="K347" t="n">
-        <v>821000</v>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D348" t="n">
-        <v>2</v>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>2303聯電</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-4.91%126</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>-4.91%</t>
-        </is>
-      </c>
-      <c r="H348" t="n">
-        <v>126</v>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>1.69%1,338,000</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="K348" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D349" t="n">
-        <v>2</v>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>3653健策</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-1.95%5770</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>-1.95%</t>
-        </is>
-      </c>
-      <c r="H349" t="n">
-        <v>5770</v>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>1.62%29,000</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="K349" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D350" t="n">
-        <v>2</v>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>2368金像電子</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>-4.08%1175</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>-4.08%</t>
-        </is>
-      </c>
-      <c r="H350" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>1.32%113,000</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="K350" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D351" t="n">
-        <v>2</v>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>3081聯亞光電</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>-0.88%3395</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>-0.88%</t>
-        </is>
-      </c>
-      <c r="H351" t="n">
-        <v>3395</v>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>1.20%37,000</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="K351" t="n">
-        <v>37000</v>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D352" t="n">
-        <v>2</v>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>2327國巨*</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>-4.93%540</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>-4.93%</t>
-        </is>
-      </c>
-      <c r="H352" t="n">
-        <v>540</v>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>1.09%202,000</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>1.09%</t>
-        </is>
-      </c>
-      <c r="K352" t="n">
-        <v>202000</v>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D353" t="n">
-        <v>2</v>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>3231緯創</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>+1.92%185.5</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>+1.92%</t>
-        </is>
-      </c>
-      <c r="H353" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>1.06%611,000</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="K353" t="n">
-        <v>611000</v>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D354" t="n">
-        <v>2</v>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>5289宜鼎國際</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>-2.07%1420</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>-2.07%</t>
-        </is>
-      </c>
-      <c r="H354" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>1.02%73,872</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="K354" t="n">
-        <v>73872</v>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D355" t="n">
-        <v>2</v>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>3008大立光電</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>+3.03%7810</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>+3.03%</t>
-        </is>
-      </c>
-      <c r="H355" t="n">
-        <v>7810</v>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>0.94%13,000</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="K355" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D356" t="n">
-        <v>2</v>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>8996高力</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>+7.66%1265</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>+7.66%</t>
-        </is>
-      </c>
-      <c r="H356" t="n">
-        <v>1265</v>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>0.92%82,000</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="K356" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:43</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D357" t="n">
-        <v>2</v>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>4958臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>-5.23%507</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>-5.23%</t>
-        </is>
-      </c>
-      <c r="H357" t="n">
-        <v>507</v>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>0.87%171,000</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="K357" t="n">
-        <v>171000</v>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D358" t="n">
-        <v>3</v>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>3264欣銓</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>-1.68%233.5</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>-1.68%</t>
-        </is>
-      </c>
-      <c r="H358" t="n">
-        <v>233.5</v>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>0.83%367,000</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="K358" t="n">
-        <v>367000</v>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D359" t="n">
-        <v>3</v>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>6805富世達</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>-7.66%2110</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>-7.66%</t>
-        </is>
-      </c>
-      <c r="H359" t="n">
-        <v>2110</v>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>0.78%36,000</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="K359" t="n">
-        <v>36000</v>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D360" t="n">
-        <v>3</v>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>6139亞翔工程</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>0%721</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H360" t="n">
-        <v>721</v>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>0.75%102,000</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="K360" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D361" t="n">
-        <v>3</v>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>7769鴻勁</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>-2.73%5710</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>-2.73%</t>
-        </is>
-      </c>
-      <c r="H361" t="n">
-        <v>5710</v>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>0.73%13,000</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>0.73%</t>
-        </is>
-      </c>
-      <c r="K361" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D362" t="n">
-        <v>3</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>2337旺宏</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>+0.41%123</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="H362" t="n">
-        <v>123</v>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>0.64%550,000</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="K362" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D363" t="n">
-        <v>3</v>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>8299群聯電子</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>-2.82%2065</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>-2.82%</t>
-        </is>
-      </c>
-      <c r="H363" t="n">
-        <v>2065</v>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>0.63%31,000</t>
-        </is>
-      </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="K363" t="n">
-        <v>31000</v>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D364" t="n">
-        <v>3</v>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>-3.44%589</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>-3.44%</t>
-        </is>
-      </c>
-      <c r="H364" t="n">
-        <v>589</v>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>0.58%100,000</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="K364" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D365" t="n">
-        <v>3</v>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>2455全新</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>+3.44%542</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>+3.44%</t>
-        </is>
-      </c>
-      <c r="H365" t="n">
-        <v>542</v>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>0.56%113,000</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="K365" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D366" t="n">
-        <v>3</v>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>8358金居開發</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>-4.37%503</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>-4.37%</t>
-        </is>
-      </c>
-      <c r="H366" t="n">
-        <v>503</v>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>0.54%108,000</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="K366" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D367" t="n">
-        <v>3</v>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>2347聯強</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>+1.63%87.4</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
-        </is>
-      </c>
-      <c r="H367" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>0.43%524,000</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="K367" t="n">
-        <v>524000</v>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D368" t="n">
-        <v>3</v>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>6147頎邦</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>-0.54%182.5</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
-        </is>
-      </c>
-      <c r="H368" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>0.30%173,000</t>
-        </is>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="K368" t="n">
-        <v>173000</v>
-      </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D369" t="n">
-        <v>3</v>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>8210勤誠興業</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>-2.22%968</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>-2.22%</t>
-        </is>
-      </c>
-      <c r="H369" t="n">
-        <v>968</v>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>0.30%32,000</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="K369" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D370" t="n">
-        <v>3</v>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>2885元大金</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>0%66.7</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H370" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>0.28%439,360</t>
-        </is>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="K370" t="n">
-        <v>439360</v>
-      </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D371" t="n">
-        <v>3</v>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>3036文曄</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>-4.59%187</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>-4.59%</t>
-        </is>
-      </c>
-      <c r="H371" t="n">
-        <v>187</v>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>0.28%149,000</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="K371" t="n">
-        <v>149000</v>
-      </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:44</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D372" t="n">
-        <v>3</v>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>2301光寶科技</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>+4.83%315</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>+4.83%</t>
-        </is>
-      </c>
-      <c r="H372" t="n">
-        <v>315</v>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>0.25%87,000</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="K372" t="n">
-        <v>87000</v>
-      </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D373" t="n">
-        <v>4</v>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>6187萬潤科技</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>-2.55%1340</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="H373" t="n">
-        <v>1340</v>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>0.25%19,000</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="K373" t="n">
-        <v>19000</v>
-      </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D374" t="n">
-        <v>4</v>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>2467志聖</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>-2.4%609</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="H374" t="n">
-        <v>609</v>
-      </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>0.24%41,000</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="K374" t="n">
-        <v>41000</v>
-      </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D375" t="n">
-        <v>4</v>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>2883凱基金控</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>+1.57%35.5</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>+1.57%</t>
-        </is>
-      </c>
-      <c r="H375" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>0.24%729,000</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="K375" t="n">
-        <v>729000</v>
-      </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D376" t="n">
-        <v>4</v>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>3131弘塑科技</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>-3.02%2405</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>-3.02%</t>
-        </is>
-      </c>
-      <c r="H376" t="n">
-        <v>2405</v>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>0.24%10,000</t>
-        </is>
-      </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="K376" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D377" t="n">
-        <v>4</v>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>3491昇達科技</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>-2.36%1445</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="H377" t="n">
-        <v>1445</v>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>0.23%16,000</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="K377" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D378" t="n">
-        <v>4</v>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>2890永豐金控</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>+1.57%42.15</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>+1.57%</t>
-        </is>
-      </c>
-      <c r="H378" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>0.22%566,220</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="K378" t="n">
-        <v>566220</v>
-      </c>
-      <c r="L378" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D379" t="n">
-        <v>4</v>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>2360致茂</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>-2.71%1975</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>-2.71%</t>
-        </is>
-      </c>
-      <c r="H379" t="n">
-        <v>1975</v>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>0.21%11,000</t>
-        </is>
-      </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="K379" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D380" t="n">
-        <v>4</v>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>3044健鼎科技</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>-0.2%502</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="H380" t="n">
-        <v>502</v>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>0.21%43,000</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="K380" t="n">
-        <v>43000</v>
-      </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D381" t="n">
-        <v>4</v>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>6239力成</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>-2.11%278</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>-2.11%</t>
-        </is>
-      </c>
-      <c r="H381" t="n">
-        <v>278</v>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>0.21%77,000</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="K381" t="n">
-        <v>77000</v>
-      </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D382" t="n">
-        <v>4</v>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>1560中砂</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>-5.38%704</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>-5.38%</t>
-        </is>
-      </c>
-      <c r="H382" t="n">
-        <v>704</v>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>0.20%28,000</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K382" t="n">
-        <v>28000</v>
-      </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D383" t="n">
-        <v>4</v>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>2395研華</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>-2.67%692</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>-2.67%</t>
-        </is>
-      </c>
-      <c r="H383" t="n">
-        <v>692</v>
-      </c>
-      <c r="I383" t="inlineStr">
-        <is>
-          <t>0.20%29,000</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K383" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D384" t="n">
-        <v>4</v>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>6584南俊國際</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>-1.35%658</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>-1.35%</t>
-        </is>
-      </c>
-      <c r="H384" t="n">
-        <v>658</v>
-      </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>0.20%32,000</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K384" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D385" t="n">
-        <v>4</v>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>2313華通</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>-1.19%249</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>-1.19%</t>
-        </is>
-      </c>
-      <c r="H385" t="n">
-        <v>249</v>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>0.19%78,000</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K385" t="n">
-        <v>78000</v>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D386" t="n">
-        <v>4</v>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>6196帆宣</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>-2.96%492</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>-2.96%</t>
-        </is>
-      </c>
-      <c r="H386" t="n">
-        <v>492</v>
-      </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>0.19%39,000</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K386" t="n">
-        <v>39000</v>
-      </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:46</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D387" t="n">
-        <v>4</v>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>6415矽力*-KY</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>+1.79%426</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>+1.79%</t>
-        </is>
-      </c>
-      <c r="H387" t="n">
-        <v>426</v>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>0.18%45,000</t>
-        </is>
-      </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="K387" t="n">
-        <v>45000</v>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:47</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D388" t="n">
-        <v>5</v>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>3042晶技</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>-1.1%180</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>-1.1%</t>
-        </is>
-      </c>
-      <c r="H388" t="n">
-        <v>180</v>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>0.17%97,000</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="K388" t="n">
-        <v>97000</v>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:47</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D389" t="n">
-        <v>5</v>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>3702大聯大</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>+1.49%102</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>+1.49%</t>
-        </is>
-      </c>
-      <c r="H389" t="n">
-        <v>102</v>
-      </c>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>0.17%177,000</t>
-        </is>
-      </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="K389" t="n">
-        <v>177000</v>
-      </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:47</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D390" t="n">
-        <v>5</v>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>6213聯茂</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>-2.55%536</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="H390" t="n">
-        <v>536</v>
-      </c>
-      <c r="I390" t="inlineStr">
-        <is>
-          <t>0.17%33,000</t>
-        </is>
-      </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="K390" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:47</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D391" t="n">
-        <v>5</v>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>2449京元電子</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>-3.05%270.5</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>-3.05%</t>
-        </is>
-      </c>
-      <c r="H391" t="n">
-        <v>270.5</v>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>0.16%59,000</t>
-        </is>
-      </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K391" t="n">
-        <v>59000</v>
-      </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:47</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D392" t="n">
-        <v>5</v>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>3661世芯-KY</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>-1.75%4200</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>-1.75%</t>
-        </is>
-      </c>
-      <c r="H392" t="n">
-        <v>4200</v>
-      </c>
-      <c r="I392" t="inlineStr">
-        <is>
-          <t>0.16%4,000</t>
-        </is>
-      </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K392" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D393" t="n">
-        <v>1</v>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>2330台積電</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>-2.25%2385</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>-2.25%</t>
-        </is>
-      </c>
-      <c r="H393" t="n">
-        <v>2385</v>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>8.55%1,034,000</t>
-        </is>
-      </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>8.55%</t>
-        </is>
-      </c>
-      <c r="K393" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D394" t="n">
-        <v>1</v>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>2454聯發科</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>-0.93%4275</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="H394" t="n">
-        <v>4275</v>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>6.97%470,000</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>6.97%</t>
-        </is>
-      </c>
-      <c r="K394" t="n">
-        <v>470000</v>
-      </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M394" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D395" t="n">
-        <v>1</v>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>6669緯穎</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>0%2610</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H395" t="n">
-        <v>2610</v>
-      </c>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>5.97%659,197</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>5.97%</t>
-        </is>
-      </c>
-      <c r="K395" t="n">
-        <v>659197</v>
-      </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D396" t="n">
-        <v>1</v>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>2059川湖</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>-2.01%13865</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-2.01%</t>
-        </is>
-      </c>
-      <c r="H396" t="n">
-        <v>13865</v>
-      </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>5.91%123,000</t>
-        </is>
-      </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>5.91%</t>
-        </is>
-      </c>
-      <c r="K396" t="n">
-        <v>123000</v>
-      </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D397" t="n">
-        <v>1</v>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>3653健策</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-1.95%5770</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-1.95%</t>
-        </is>
-      </c>
-      <c r="H397" t="n">
-        <v>5770</v>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>4.42%221,000</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>4.42%</t>
-        </is>
-      </c>
-      <c r="K397" t="n">
-        <v>221000</v>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D398" t="n">
-        <v>1</v>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>6223旺矽</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>-2.22%5290</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>-2.22%</t>
-        </is>
-      </c>
-      <c r="H398" t="n">
-        <v>5290</v>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>4.37%238,000</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>4.37%</t>
-        </is>
-      </c>
-      <c r="K398" t="n">
-        <v>238000</v>
-      </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D399" t="n">
-        <v>1</v>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>3008大立光</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>+3.03%7810</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>+3.03%</t>
-        </is>
-      </c>
-      <c r="H399" t="n">
-        <v>7810</v>
-      </c>
-      <c r="I399" t="inlineStr">
-        <is>
-          <t>4.17%154,000</t>
-        </is>
-      </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="K399" t="n">
-        <v>154000</v>
-      </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>+0.12%</t>
-        </is>
-      </c>
-      <c r="M399" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D400" t="n">
-        <v>1</v>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>3443創意</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>-1.67%5895</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>-1.67%</t>
-        </is>
-      </c>
-      <c r="H400" t="n">
-        <v>5895</v>
-      </c>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>3.88%190,000</t>
-        </is>
-      </c>
-      <c r="J400" t="inlineStr">
-        <is>
-          <t>3.88%</t>
-        </is>
-      </c>
-      <c r="K400" t="n">
-        <v>190000</v>
-      </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D401" t="n">
-        <v>1</v>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>3017奇鋐</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>-2.93%3310</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>-2.93%</t>
-        </is>
-      </c>
-      <c r="H401" t="n">
-        <v>3310</v>
-      </c>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>3.86%336,000</t>
-        </is>
-      </c>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>3.86%</t>
-        </is>
-      </c>
-      <c r="K401" t="n">
-        <v>336000</v>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D402" t="n">
-        <v>1</v>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>5274信 驊</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>+3.53%17725</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>+3.53%</t>
-        </is>
-      </c>
-      <c r="H402" t="n">
-        <v>17725</v>
-      </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>3.22%52,400</t>
-        </is>
-      </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>3.22%</t>
-        </is>
-      </c>
-      <c r="K402" t="n">
-        <v>52400</v>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D403" t="n">
-        <v>1</v>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>2360致茂</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>-2.71%1975</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>-2.71%</t>
-        </is>
-      </c>
-      <c r="H403" t="n">
-        <v>1975</v>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>3.22%470,000</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>3.22%</t>
-        </is>
-      </c>
-      <c r="K403" t="n">
-        <v>470000</v>
-      </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D404" t="n">
-        <v>1</v>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>6488環球晶</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>-2.72%967</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>-2.72%</t>
-        </is>
-      </c>
-      <c r="H404" t="n">
-        <v>967</v>
-      </c>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>3.15%938,000</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>3.15%</t>
-        </is>
-      </c>
-      <c r="K404" t="n">
-        <v>938000</v>
-      </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D405" t="n">
-        <v>1</v>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>3037欣興</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>+0.21%973</t>
-        </is>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="H405" t="n">
-        <v>973</v>
-      </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>3.06%907,000</t>
-        </is>
-      </c>
-      <c r="J405" t="inlineStr">
-        <is>
-          <t>3.06%</t>
-        </is>
-      </c>
-      <c r="K405" t="n">
-        <v>907000</v>
-      </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
-        <v>1</v>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>6187萬 潤</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>-2.55%1340</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="H406" t="n">
-        <v>1340</v>
-      </c>
-      <c r="I406" t="inlineStr">
-        <is>
-          <t>2.77%596,000</t>
-        </is>
-      </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>2.77%</t>
-        </is>
-      </c>
-      <c r="K406" t="n">
-        <v>596000</v>
-      </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:53</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D407" t="n">
-        <v>1</v>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>2308台達電</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>-7.24%1730</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>-7.24%</t>
-        </is>
-      </c>
-      <c r="H407" t="n">
-        <v>1730</v>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>2.68%446,000</t>
-        </is>
-      </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>2.68%</t>
-        </is>
-      </c>
-      <c r="K407" t="n">
-        <v>446000</v>
-      </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>2</v>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>2383台光電</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>-3.46%5445</t>
-        </is>
-      </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>-3.46%</t>
-        </is>
-      </c>
-      <c r="H408" t="n">
-        <v>5445</v>
-      </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>2.32%123,000</t>
-        </is>
-      </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>2.32%</t>
-        </is>
-      </c>
-      <c r="K408" t="n">
-        <v>123000</v>
-      </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>2</v>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>6274台 燿</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>-2.76%1410</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>-2.76%</t>
-        </is>
-      </c>
-      <c r="H409" t="n">
-        <v>1410</v>
-      </c>
-      <c r="I409" t="inlineStr">
-        <is>
-          <t>1.93%395,000</t>
-        </is>
-      </c>
-      <c r="J409" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="K409" t="n">
-        <v>395000</v>
-      </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D410" t="n">
-        <v>2</v>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>3044健鼎</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>-0.2%502</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="H410" t="n">
-        <v>502</v>
-      </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>1.80%1,034,000</t>
-        </is>
-      </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="K410" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D411" t="n">
-        <v>2</v>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>3665貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>-6.26%2170</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>-6.26%</t>
-        </is>
-      </c>
-      <c r="H411" t="n">
-        <v>2170</v>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>1.72%228,000</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>1.72%</t>
-        </is>
-      </c>
-      <c r="K411" t="n">
-        <v>228000</v>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D412" t="n">
-        <v>2</v>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>2345智邦</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>-2.95%2140</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
-        </is>
-      </c>
-      <c r="H412" t="n">
-        <v>2140</v>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>1.68%227,000</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="K412" t="n">
-        <v>227000</v>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D413" t="n">
-        <v>2</v>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>2881富邦金</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>-1.03%143.5</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>-1.03%</t>
-        </is>
-      </c>
-      <c r="H413" t="n">
-        <v>143.5</v>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>1.54%3,104,000</t>
-        </is>
-      </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>1.54%</t>
-        </is>
-      </c>
-      <c r="K413" t="n">
-        <v>3104000</v>
-      </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D414" t="n">
-        <v>2</v>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>1303南亞</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>+1.28%237.5</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>+1.28%</t>
-        </is>
-      </c>
-      <c r="H414" t="n">
-        <v>237.5</v>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>1.53%1,861,000</t>
-        </is>
-      </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>1.53%</t>
-        </is>
-      </c>
-      <c r="K414" t="n">
-        <v>1861000</v>
-      </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D415" t="n">
-        <v>2</v>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>2885元大金</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>0%66.7</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H415" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>1.45%6,267,040</t>
-        </is>
-      </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>1.45%</t>
-        </is>
-      </c>
-      <c r="K415" t="n">
-        <v>6267040</v>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D416" t="n">
-        <v>2</v>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>2368金像電</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>-4.08%1175</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>-4.08%</t>
-        </is>
-      </c>
-      <c r="H416" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>1.44%353,000</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>1.44%</t>
-        </is>
-      </c>
-      <c r="K416" t="n">
-        <v>353000</v>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D417" t="n">
-        <v>2</v>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>6442光 聖</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>+9.79%1795</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>+9.79%</t>
-        </is>
-      </c>
-      <c r="H417" t="n">
-        <v>1795</v>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>1.01%163,000</t>
-        </is>
-      </c>
-      <c r="J417" t="inlineStr">
-        <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="K417" t="n">
-        <v>163000</v>
-      </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D418" t="n">
-        <v>2</v>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>3529力旺</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>-9.28%2395</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>-9.28%</t>
-        </is>
-      </c>
-      <c r="H418" t="n">
-        <v>2395</v>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>1.01%122,000</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="K418" t="n">
-        <v>122000</v>
-      </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>2</v>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>3036文曄</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>-4.59%187</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>-4.59%</t>
-        </is>
-      </c>
-      <c r="H419" t="n">
-        <v>187</v>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>0.99%1,532,000</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="K419" t="n">
-        <v>1532000</v>
-      </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D420" t="n">
-        <v>2</v>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>7750新 代</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>-1.92%2300</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>-1.92%</t>
-        </is>
-      </c>
-      <c r="H420" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>0.97%122,000</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>0.97%</t>
-        </is>
-      </c>
-      <c r="K420" t="n">
-        <v>122000</v>
-      </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D421" t="n">
-        <v>2</v>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>3081聯 亞</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>-0.88%3395</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>-0.88%</t>
-        </is>
-      </c>
-      <c r="H421" t="n">
-        <v>3395</v>
-      </c>
-      <c r="I421" t="inlineStr">
-        <is>
-          <t>0.97%82,000</t>
-        </is>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>0.97%</t>
-        </is>
-      </c>
-      <c r="K421" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:54</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>2</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>3026禾伸堂</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>-6.16%686</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>-6.16%</t>
-        </is>
-      </c>
-      <c r="H422" t="n">
-        <v>686</v>
-      </c>
-      <c r="I422" t="inlineStr">
-        <is>
-          <t>0.96%404,000</t>
-        </is>
-      </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="K422" t="n">
-        <v>404000</v>
-      </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M422" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>3</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>2313華通</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>-1.19%249</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>-1.19%</t>
-        </is>
-      </c>
-      <c r="H423" t="n">
-        <v>249</v>
-      </c>
-      <c r="I423" t="inlineStr">
-        <is>
-          <t>0.96%1,107,336</t>
-        </is>
-      </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="K423" t="n">
-        <v>1107336</v>
-      </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M423" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>3</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>-3.44%589</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>-3.44%</t>
-        </is>
-      </c>
-      <c r="H424" t="n">
-        <v>589</v>
-      </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>0.95%464,000</t>
-        </is>
-      </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="K424" t="n">
-        <v>464000</v>
-      </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>3</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>2449京元電子</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>-3.05%270.5</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>-3.05%</t>
-        </is>
-      </c>
-      <c r="H425" t="n">
-        <v>270.5</v>
-      </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>0.94%999,000</t>
-        </is>
-      </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="K425" t="n">
-        <v>999000</v>
-      </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M425" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>3</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>2303聯電</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>-4.91%126</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>-4.91%</t>
-        </is>
-      </c>
-      <c r="H426" t="n">
-        <v>126</v>
-      </c>
-      <c r="I426" t="inlineStr">
-        <is>
-          <t>0.92%2,096,000</t>
-        </is>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="K426" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>3</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>2317鴻海</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>-1.95%251</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>-1.95%</t>
-        </is>
-      </c>
-      <c r="H427" t="n">
-        <v>251</v>
-      </c>
-      <c r="I427" t="inlineStr">
-        <is>
-          <t>0.84%960,000</t>
-        </is>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="K427" t="n">
-        <v>960000</v>
-      </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>3</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>2382廣達</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>-1.46%337</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>-1.46%</t>
-        </is>
-      </c>
-      <c r="H428" t="n">
-        <v>337</v>
-      </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>0.78%664,000</t>
-        </is>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="K428" t="n">
-        <v>664000</v>
-      </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>3</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>5347世界先進</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>-2.61%149.5</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>-2.61%</t>
-        </is>
-      </c>
-      <c r="H429" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>0.70%1,351,000</t>
-        </is>
-      </c>
-      <c r="J429" t="inlineStr">
-        <is>
-          <t>0.70%</t>
-        </is>
-      </c>
-      <c r="K429" t="n">
-        <v>1351000</v>
-      </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>3</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>4979華星光</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>+4%624</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>+4%</t>
-        </is>
-      </c>
-      <c r="H430" t="n">
-        <v>624</v>
-      </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>0.63%293,000</t>
-        </is>
-      </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="K430" t="n">
-        <v>293000</v>
-      </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M430" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>3</v>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>6515穎崴</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>+2.03%7050</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>+2.03%</t>
-        </is>
-      </c>
-      <c r="H431" t="n">
-        <v>7050</v>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>0.51%21,000</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="K431" t="n">
-        <v>21000</v>
-      </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>3</v>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>3374精 材</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>-0.47%419.5</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="H432" t="n">
-        <v>419.5</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>0.49%340,000</t>
-        </is>
-      </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="K432" t="n">
-        <v>340000</v>
-      </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>3</v>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>7769鴻 勁</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>-2.73%5710</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>-2.73%</t>
-        </is>
-      </c>
-      <c r="H433" t="n">
-        <v>5710</v>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>0.40%20,000</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="K433" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>3</v>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>5434崇越</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>-0.93%535</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="H434" t="n">
-        <v>535</v>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>0.37%200,000</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="K434" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>3</v>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>3090日電貿</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>-2.6%168.5</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
-      <c r="H435" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>0.35%592,000</t>
-        </is>
-      </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="K435" t="n">
-        <v>592000</v>
-      </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>3</v>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>3293鈊 象</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>-0.42%708</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-0.42%</t>
-        </is>
-      </c>
-      <c r="H436" t="n">
-        <v>708</v>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>0.33%133,000</t>
-        </is>
-      </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="K436" t="n">
-        <v>133000</v>
-      </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:35:56</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>3</v>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>3167大 量</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>-3.25%774</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>-3.25%</t>
-        </is>
-      </c>
-      <c r="H437" t="n">
-        <v>774</v>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>0.31%115,000</t>
-        </is>
-      </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>0.31%</t>
-        </is>
-      </c>
-      <c r="K437" t="n">
-        <v>115000</v>
-      </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M437" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-03_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-03_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:12</t>
+          <t>2026-09-03 23:01:27</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28615,7 +28615,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28741,7 +28741,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28989,7 +28989,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29172,7 +29172,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29294,7 +29294,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29416,7 +29416,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29538,7 +29538,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:38</t>
+          <t>2026-09-03 23:01:55</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29965,7 +29965,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30209,7 +30209,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30331,7 +30331,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30575,7 +30575,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:40</t>
+          <t>2026-09-03 23:01:56</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30880,7 +30880,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -31002,7 +31002,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31063,7 +31063,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31124,7 +31124,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31246,7 +31246,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31429,7 +31429,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31490,7 +31490,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:41</t>
+          <t>2026-09-03 23:01:57</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:42</t>
+          <t>2026-09-03 23:01:59</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:42</t>
+          <t>2026-09-03 23:01:59</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31734,7 +31734,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:42</t>
+          <t>2026-09-03 23:01:59</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:42</t>
+          <t>2026-09-03 23:01:59</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:42</t>
+          <t>2026-09-03 23:01:59</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31917,7 +31917,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31978,7 +31978,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32161,7 +32161,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32222,7 +32222,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32283,7 +32283,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32344,7 +32344,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32527,7 +32527,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32588,7 +32588,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32649,7 +32649,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32771,7 +32771,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:48</t>
+          <t>2026-09-03 23:02:05</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32893,7 +32893,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32954,7 +32954,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33015,7 +33015,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33076,7 +33076,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33137,7 +33137,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33198,7 +33198,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33320,7 +33320,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33381,7 +33381,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33442,7 +33442,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33564,7 +33564,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33625,7 +33625,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:50</t>
+          <t>2026-09-03 23:02:06</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33808,7 +33808,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33869,7 +33869,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33930,7 +33930,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34235,7 +34235,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34357,7 +34357,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -34540,7 +34540,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:51</t>
+          <t>2026-09-03 23:02:07</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
